--- a/artfynd/A 10792-2026 artfynd.xlsx
+++ b/artfynd/A 10792-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102173060</v>
+        <v>105157102</v>
       </c>
       <c r="B2" t="n">
-        <v>12448</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101691</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stormyran, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604732.1031514951</v>
+        <v>604687</v>
       </c>
       <c r="R2" t="n">
-        <v>7021006.860857152</v>
+        <v>7020973</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,64 +743,47 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Larv cirka 1 cm lång. Naturskog</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105157102</v>
+        <v>105157116</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -842,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604686.3592666471</v>
+        <v>604703</v>
       </c>
       <c r="R3" t="n">
-        <v>7020972.520558505</v>
+        <v>7020954</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,19 +844,14 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105157105</v>
+        <v>105165164</v>
       </c>
       <c r="B4" t="n">
-        <v>12448</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101691</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604749.2560601905</v>
+        <v>604685</v>
       </c>
       <c r="R4" t="n">
-        <v>7020992.120277546</v>
+        <v>7020888</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,27 +947,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Larv på granlåga, naturskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,50 +988,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105165164</v>
+        <v>102173060</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>101691</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.Sahlberg, 1875</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604684.6260009914</v>
+        <v>604732</v>
       </c>
       <c r="R5" t="n">
-        <v>7020887.413752369</v>
+        <v>7021007</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,27 +1062,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Larv cirka 1 cm lång. Naturskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,37 +1081,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>105157104</v>
       </c>
       <c r="B6" t="n">
-        <v>12448</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604742.1377964704</v>
+        <v>604742</v>
       </c>
       <c r="R6" t="n">
-        <v>7021003.138041172</v>
+        <v>7021003</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1233,19 +1168,9 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1281,37 +1206,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105157116</v>
+        <v>105157105</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>101691</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.Sahlberg, 1875</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1321,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604702.7437038994</v>
+        <v>604749</v>
       </c>
       <c r="R7" t="n">
-        <v>7020953.704553189</v>
+        <v>7020992</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1354,24 +1274,14 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Larv på granlåga, naturskog</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 10792-2026 artfynd.xlsx
+++ b/artfynd/A 10792-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105157102</v>
+        <v>134687261</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604687</v>
+        <v>604681</v>
       </c>
       <c r="R2" t="n">
-        <v>7020973</v>
+        <v>7020987</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,61 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105157116</v>
+        <v>134687230</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604703</v>
+        <v>604677</v>
       </c>
       <c r="R3" t="n">
-        <v>7020954</v>
+        <v>7020993</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -841,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,61 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105165164</v>
+        <v>134687231</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604685</v>
+        <v>604694</v>
       </c>
       <c r="R4" t="n">
-        <v>7020888</v>
+        <v>7021028</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -947,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,70 +954,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102173060</v>
+        <v>134687229</v>
       </c>
       <c r="B5" t="n">
-        <v>12564</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101691</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604732</v>
+        <v>604685</v>
       </c>
       <c r="R5" t="n">
-        <v>7021007</v>
+        <v>7020959</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1062,17 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Larv cirka 1 cm lång. Naturskog</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105157104</v>
+        <v>105157102</v>
       </c>
       <c r="B6" t="n">
-        <v>12564</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101691</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604742</v>
+        <v>604687</v>
       </c>
       <c r="R6" t="n">
-        <v>7021003</v>
+        <v>7020973</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1171,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Larv, naturskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105157105</v>
+        <v>105157116</v>
       </c>
       <c r="B7" t="n">
-        <v>12564</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101691</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604749</v>
+        <v>604703</v>
       </c>
       <c r="R7" t="n">
-        <v>7020992</v>
+        <v>7020954</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1281,7 +1239,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Larv på granlåga, naturskog</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,6 +1267,3217 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>105165164</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>604685</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7020888</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134687241</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>604652</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7021110</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134687242</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>604647</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7021080</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134687243</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>604661</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7021026</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134687244</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>604670</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7021009</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134687245</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>604678</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7020938</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134687246</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>604630</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7020941</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134687247</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>604666</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7021055</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134687248</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>604681</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7020987</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134687249</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>604683</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7020999</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134687250</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>604684</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7021008</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134687251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>604688</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7021025</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134687252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>604709</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7021039</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134687253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>604749</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7021027</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134687254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>604755</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7021003</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134687255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>604705</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7020966</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134687256</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>604686</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7020963</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134687257</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>604680</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7020934</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134687258</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>604666</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7020926</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134687232</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79397</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>604756</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7021003</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134687240</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>604704</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7020992</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134687234</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>604723</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7021040</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134687235</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>604734</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7021048</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134687236</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>604649</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7021124</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134687237</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>604725</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7021044</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134687238</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>604738</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7021055</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>102173060</v>
+      </c>
+      <c r="B34" t="n">
+        <v>12564</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101691</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre barkplattbagge</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pytho abieticola</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>J.Sahlberg, 1875</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>604732</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7021007</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Larv cirka 1 cm lång. Naturskog</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>105157104</v>
+      </c>
+      <c r="B35" t="n">
+        <v>12564</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>101691</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre barkplattbagge</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pytho abieticola</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>J.Sahlberg, 1875</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>604742</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7021003</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Larv, naturskog</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>105157105</v>
+      </c>
+      <c r="B36" t="n">
+        <v>12564</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>101691</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mindre barkplattbagge</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pytho abieticola</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>J.Sahlberg, 1875</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>604749</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7020992</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Larv på granlåga, naturskog</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134687260</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>604733</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7021049</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134687239</v>
+      </c>
+      <c r="B38" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>604683</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7020925</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134687233</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>604700</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7020997</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10792-2026 artfynd.xlsx
+++ b/artfynd/A 10792-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687261</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687230</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687231</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687229</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157102</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157116</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105165164</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1470,6 +1510,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687241</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,6 +1612,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687242</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,6 +1714,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687243</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1761,6 +1816,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687244</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1858,6 +1918,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687245</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1955,6 +2020,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687246</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2057,6 +2127,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687247</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2159,6 +2234,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687248</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2261,6 +2341,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687249</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2363,6 +2448,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687250</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2465,6 +2555,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687251</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2567,6 +2662,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687252</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2669,6 +2769,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687253</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2771,6 +2876,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687254</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2873,6 +2983,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687255</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2975,6 +3090,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687256</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3077,6 +3197,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687257</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3179,6 +3304,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687258</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3276,6 +3406,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687232</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3373,6 +3508,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687240</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3470,6 +3610,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687234</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3567,6 +3712,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687235</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3669,6 +3819,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687236</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3766,6 +3921,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687237</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3863,6 +4023,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687238</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3975,6 +4140,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102173060</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4081,6 +4251,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157104</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4187,6 +4362,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157105</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4284,6 +4464,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687260</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4381,6 +4566,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687239</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4478,8 +4668,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134687233</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>